--- a/artfynd/A 21371-2026 artfynd.xlsx
+++ b/artfynd/A 21371-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118237709</v>
+        <v>118237708</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526615</v>
+        <v>526499</v>
       </c>
       <c r="R2" t="n">
-        <v>6980405</v>
+        <v>6980474</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118237710</v>
+        <v>118237709</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526625</v>
+        <v>526615</v>
       </c>
       <c r="R3" t="n">
-        <v>6980402</v>
+        <v>6980405</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,6 +894,117 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118237710</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>HÃ¥vdsjÃ¶, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>526625</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6980402</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
